--- a/jogos_2025-08-30.xlsx
+++ b/jogos_2025-08-30.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kolos Kovalivka</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9087,10 +9087,10 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kolos Kovalivka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9474,10 +9474,10 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Y70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="M87" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>2.2</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11808,10 +11808,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12582,10 +12582,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,22 +18564,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20064,10 +20064,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20322,10 +20322,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,16 +21477,16 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z163" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21960,7 +21960,7 @@
         <v>3.55</v>
       </c>
       <c r="N167" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z173" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,22 +23724,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,16 +25734,16 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z196" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26340,13 +26340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26379,10 +26379,10 @@
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z201" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26469,13 +26469,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -26508,10 +26508,10 @@
         <v>0</v>
       </c>
       <c r="Y202" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z202" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA202" t="n">
         <v>0</v>
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="M207" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N207" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27153,10 +27153,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,22 +27723,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,22 +28368,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Badalona</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,22 +28884,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,22 +29013,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Badalona</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30771,10 +30771,10 @@
         <v>0</v>
       </c>
       <c r="AA235" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB235" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC235" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -30984,13 +30984,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>3.31</v>
+        <v>2.13</v>
       </c>
       <c r="M237" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N237" t="n">
-        <v>2.17</v>
+        <v>3.45</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z237" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="M238" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N238" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="Z238" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,55 +31371,55 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="M240" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="N240" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" t="n">
+        <v>0</v>
+      </c>
+      <c r="W240" t="n">
+        <v>0</v>
+      </c>
+      <c r="X240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB240" t="n">
         <v>1.8</v>
-      </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="n">
-        <v>0</v>
-      </c>
-      <c r="T240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="n">
-        <v>0</v>
-      </c>
-      <c r="V240" t="n">
-        <v>0</v>
-      </c>
-      <c r="W240" t="n">
-        <v>0</v>
-      </c>
-      <c r="X240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y240" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z240" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA240" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB240" t="n">
-        <v>0</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="M241" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N241" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31539,10 +31539,10 @@
         <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="Z241" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AA241" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="M244" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N244" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Z244" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31980,22 +31980,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,22 +33786,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z263" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34947,22 +34947,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35373,10 +35373,10 @@
         <v>1.08</v>
       </c>
       <c r="M271" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="N271" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,22 +35592,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z277" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z278" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36570,10 +36570,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z285" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37398,22 +37398,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37527,22 +37527,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,22 +37656,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,10 +37860,10 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z290" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA290" t="n">
         <v>0</v>
@@ -37914,22 +37914,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,10 +38505,10 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z295" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA295" t="n">
         <v>0</v>
@@ -38559,7 +38559,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -38569,12 +38569,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38595,13 +38595,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -38634,10 +38634,10 @@
         <v>0</v>
       </c>
       <c r="Y296" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z296" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA296" t="n">
         <v>0</v>
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38724,13 +38724,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -38763,10 +38763,10 @@
         <v>0</v>
       </c>
       <c r="Y297" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z297" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA297" t="n">
         <v>0</v>
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38853,13 +38853,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M298" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -38892,10 +38892,10 @@
         <v>0</v>
       </c>
       <c r="Y298" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z298" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA298" t="n">
         <v>0</v>
@@ -38946,22 +38946,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39075,7 +39075,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39333,22 +39333,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39369,13 +39369,13 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N302" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O302" t="n">
         <v>0</v>
@@ -39408,10 +39408,10 @@
         <v>0</v>
       </c>
       <c r="Y302" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z302" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA302" t="n">
         <v>0</v>
@@ -39591,22 +39591,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -39988,12 +39988,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40236,22 +40236,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N309" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O309" t="n">
         <v>0</v>
@@ -40311,10 +40311,10 @@
         <v>0</v>
       </c>
       <c r="Y309" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z309" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA309" t="n">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40401,13 +40401,13 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M310" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N310" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
@@ -40440,10 +40440,10 @@
         <v>0</v>
       </c>
       <c r="Y310" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z310" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA310" t="n">
         <v>0</v>
@@ -40494,22 +40494,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40530,13 +40530,13 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M311" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N311" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -40569,10 +40569,10 @@
         <v>0</v>
       </c>
       <c r="Y311" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z311" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA311" t="n">
         <v>0</v>
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41278,12 +41278,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41655,7 +41655,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -41794,12 +41794,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -42171,7 +42171,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -42181,12 +42181,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -42300,7 +42300,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -42568,12 +42568,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -42697,12 +42697,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -42826,12 +42826,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -43074,7 +43074,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -43084,12 +43084,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -43110,13 +43110,13 @@
         </is>
       </c>
       <c r="L331" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M331" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N331" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O331" t="n">
         <v>0</v>
@@ -43149,10 +43149,10 @@
         <v>0</v>
       </c>
       <c r="Y331" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z331" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA331" t="n">
         <v>0</v>
@@ -43203,7 +43203,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -43213,12 +43213,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -43239,13 +43239,13 @@
         </is>
       </c>
       <c r="L332" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M332" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N332" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O332" t="n">
         <v>0</v>
@@ -43278,10 +43278,10 @@
         <v>0</v>
       </c>
       <c r="Y332" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z332" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA332" t="n">
         <v>0</v>
@@ -43342,12 +43342,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -43471,12 +43471,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -43497,22 +43497,22 @@
         </is>
       </c>
       <c r="L334" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N334" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O334" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P334" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q334" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R334" t="n">
         <v>0</v>
@@ -43536,10 +43536,10 @@
         <v>0</v>
       </c>
       <c r="Y334" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z334" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA334" t="n">
         <v>0</v>
@@ -43570,10 +43570,10 @@
         <v>0</v>
       </c>
       <c r="AI334" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ334" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK334" s="3" t="n">
         <v>45899.79166666666</v>
@@ -43729,12 +43729,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -43858,12 +43858,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -43987,12 +43987,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -44013,22 +44013,22 @@
         </is>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M338" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N338" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O338" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q338" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R338" t="n">
         <v>0</v>
@@ -44052,10 +44052,10 @@
         <v>0</v>
       </c>
       <c r="Y338" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z338" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA338" t="n">
         <v>0</v>
@@ -44086,10 +44086,10 @@
         <v>0</v>
       </c>
       <c r="AI338" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ338" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK338" s="3" t="n">
         <v>45899.79166666666</v>
@@ -44106,7 +44106,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -44116,12 +44116,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -44245,12 +44245,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -44364,7 +44364,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -44374,12 +44374,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -44632,12 +44632,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -44751,7 +44751,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -44890,12 +44890,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -44916,13 +44916,13 @@
         </is>
       </c>
       <c r="L345" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N345" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O345" t="n">
         <v>0</v>
@@ -44961,10 +44961,10 @@
         <v>0</v>
       </c>
       <c r="AA345" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB345" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC345" t="n">
         <v>0</v>
@@ -45009,7 +45009,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -45019,12 +45019,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -45148,12 +45148,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -45174,10 +45174,10 @@
         </is>
       </c>
       <c r="L347" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="M347" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N347" t="n">
         <v>3.4</v>
@@ -45267,7 +45267,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -45277,12 +45277,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -45406,12 +45406,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -45432,13 +45432,13 @@
         </is>
       </c>
       <c r="L349" t="n">
-        <v>1.43</v>
+        <v>2.39</v>
       </c>
       <c r="M349" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N349" t="n">
-        <v>5.8</v>
+        <v>2.47</v>
       </c>
       <c r="O349" t="n">
         <v>0</v>
@@ -45480,7 +45480,7 @@
         <v>2.3</v>
       </c>
       <c r="AB349" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC349" t="n">
         <v>0</v>
@@ -45654,7 +45654,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -45664,12 +45664,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -45690,13 +45690,13 @@
         </is>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M351" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N351" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O351" t="n">
         <v>0</v>
@@ -45729,10 +45729,10 @@
         <v>0</v>
       </c>
       <c r="Y351" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z351" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA351" t="n">
         <v>0</v>
@@ -45783,7 +45783,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -45793,12 +45793,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -45819,13 +45819,13 @@
         </is>
       </c>
       <c r="L352" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N352" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O352" t="n">
         <v>0</v>
@@ -45864,10 +45864,10 @@
         <v>0</v>
       </c>
       <c r="AA352" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB352" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC352" t="n">
         <v>0</v>
@@ -45922,12 +45922,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -45948,13 +45948,13 @@
         </is>
       </c>
       <c r="L353" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="M353" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N353" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O353" t="n">
         <v>0</v>
@@ -45987,16 +45987,16 @@
         <v>0</v>
       </c>
       <c r="Y353" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB353" t="n">
         <v>1.55</v>
-      </c>
-      <c r="Z353" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA353" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB353" t="n">
-        <v>0</v>
       </c>
       <c r="AC353" t="n">
         <v>0</v>
@@ -46041,7 +46041,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -46051,12 +46051,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -46077,13 +46077,13 @@
         </is>
       </c>
       <c r="L354" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M354" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N354" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O354" t="n">
         <v>0</v>
@@ -46122,10 +46122,10 @@
         <v>0</v>
       </c>
       <c r="AA354" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB354" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC354" t="n">
         <v>0</v>
@@ -46170,7 +46170,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -46180,12 +46180,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -46206,13 +46206,13 @@
         </is>
       </c>
       <c r="L355" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M355" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N355" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O355" t="n">
         <v>0</v>
@@ -46245,10 +46245,10 @@
         <v>0</v>
       </c>
       <c r="Y355" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z355" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA355" t="n">
         <v>0</v>
@@ -46299,7 +46299,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -46309,12 +46309,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -46335,13 +46335,13 @@
         </is>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M356" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N356" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O356" t="n">
         <v>0</v>
@@ -46374,10 +46374,10 @@
         <v>0</v>
       </c>
       <c r="Y356" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z356" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA356" t="n">
         <v>0</v>
@@ -46438,12 +46438,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -46464,13 +46464,13 @@
         </is>
       </c>
       <c r="L357" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="M357" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N357" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="O357" t="n">
         <v>0</v>
@@ -46509,10 +46509,10 @@
         <v>2.3</v>
       </c>
       <c r="AA357" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB357" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC357" t="n">
         <v>0</v>
@@ -46567,12 +46567,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -46593,13 +46593,13 @@
         </is>
       </c>
       <c r="L358" t="n">
-        <v>1.96</v>
+        <v>1.46</v>
       </c>
       <c r="M358" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="N358" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="O358" t="n">
         <v>0</v>
@@ -46632,16 +46632,16 @@
         <v>0</v>
       </c>
       <c r="Y358" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA358" t="n">
         <v>2.3</v>
       </c>
-      <c r="AA358" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AB358" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC358" t="n">
         <v>0</v>
@@ -46696,12 +46696,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -46722,13 +46722,13 @@
         </is>
       </c>
       <c r="L359" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="M359" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N359" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="O359" t="n">
         <v>0</v>
@@ -46761,16 +46761,16 @@
         <v>0</v>
       </c>
       <c r="Y359" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z359" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA359" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB359" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC359" t="n">
         <v>0</v>
@@ -46825,12 +46825,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -46851,13 +46851,13 @@
         </is>
       </c>
       <c r="L360" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="M360" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="N360" t="n">
-        <v>5.2</v>
+        <v>3.35</v>
       </c>
       <c r="O360" t="n">
         <v>0</v>
@@ -46954,12 +46954,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -46980,13 +46980,13 @@
         </is>
       </c>
       <c r="L361" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="M361" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N361" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="O361" t="n">
         <v>0</v>
@@ -47083,12 +47083,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G362" t="n">
@@ -47212,12 +47212,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -47589,7 +47589,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -47599,12 +47599,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -47625,13 +47625,13 @@
         </is>
       </c>
       <c r="L366" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N366" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O366" t="n">
         <v>0</v>
@@ -47670,10 +47670,10 @@
         <v>0</v>
       </c>
       <c r="AA366" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB366" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC366" t="n">
         <v>0</v>
@@ -47718,7 +47718,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -47728,12 +47728,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -47754,13 +47754,13 @@
         </is>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M367" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N367" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O367" t="n">
         <v>0</v>
@@ -47799,10 +47799,10 @@
         <v>0</v>
       </c>
       <c r="AA367" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB367" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC367" t="n">
         <v>0</v>
@@ -47847,7 +47847,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -47857,12 +47857,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -47883,13 +47883,13 @@
         </is>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M368" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N368" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O368" t="n">
         <v>0</v>
@@ -47922,10 +47922,10 @@
         <v>0</v>
       </c>
       <c r="Y368" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z368" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA368" t="n">
         <v>0</v>
@@ -47976,7 +47976,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -47986,12 +47986,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -48012,13 +48012,13 @@
         </is>
       </c>
       <c r="L369" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N369" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O369" t="n">
         <v>0</v>
@@ -48051,10 +48051,10 @@
         <v>0</v>
       </c>
       <c r="Y369" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z369" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA369" t="n">
         <v>0</v>

--- a/jogos_2025-08-30.xlsx
+++ b/jogos_2025-08-30.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Smorgon</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>MKK-Dnepr</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Smorgon</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MKK-Dnepr</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,16 +11544,16 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11679,10 +11679,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.1</v>
+        <v>1.77</v>
       </c>
       <c r="M88" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N88" t="n">
-        <v>2.17</v>
+        <v>4.3</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11811,7 +11811,7 @@
         <v>2.2</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12195,10 +12195,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="M103" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N103" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20064,10 +20064,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20322,10 +20322,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,16 +21477,16 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z163" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z182" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,22 +23982,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24573,10 +24573,10 @@
         <v>0</v>
       </c>
       <c r="Y187" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z187" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,16 +24831,16 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z189" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -24960,10 +24960,10 @@
         <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,22 +26046,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>BATE</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,22 +26175,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>BATE</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26469,13 +26469,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -26508,10 +26508,10 @@
         <v>0</v>
       </c>
       <c r="Y202" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z202" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA202" t="n">
         <v>0</v>
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -26985,13 +26985,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27024,10 +27024,10 @@
         <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA206" t="n">
         <v>0</v>
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Badalona</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,22 +27594,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Badalona</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z236" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -30984,13 +30984,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>3.31</v>
+        <v>2.13</v>
       </c>
       <c r="M239" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N239" t="n">
-        <v>2.17</v>
+        <v>3.45</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z239" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>7.6</v>
+        <v>3.31</v>
       </c>
       <c r="M240" t="n">
-        <v>5.6</v>
+        <v>3.54</v>
       </c>
       <c r="N240" t="n">
-        <v>1.35</v>
+        <v>2.17</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,16 +31410,16 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z240" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -31593,22 +31593,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31629,13 +31629,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -31674,10 +31674,10 @@
         <v>0</v>
       </c>
       <c r="AA242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB242" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC242" t="n">
         <v>0</v>
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31758,13 +31758,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -31797,10 +31797,10 @@
         <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z243" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA243" t="n">
         <v>0</v>
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,22 +33786,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Torpedo BelAZ</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Dinamo Brest</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z264" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA264" t="n">
         <v>0</v>
@@ -34560,22 +34560,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Torpedo BelAZ</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Dinamo Brest</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34947,22 +34947,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35022,10 +35022,10 @@
         <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z268" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AA268" t="n">
         <v>0</v>
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35112,13 +35112,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36366,22 +36366,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36918,13 +36918,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37140,22 +37140,22 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37398,22 +37398,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,22 +37656,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37914,22 +37914,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M295" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,10 +38505,10 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z295" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA295" t="n">
         <v>0</v>
@@ -38817,7 +38817,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -38827,12 +38827,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38853,13 +38853,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N298" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -38892,10 +38892,10 @@
         <v>0</v>
       </c>
       <c r="Y298" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z298" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA298" t="n">
         <v>0</v>
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39075,22 +39075,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39333,22 +39333,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39369,13 +39369,13 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N302" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O302" t="n">
         <v>0</v>
@@ -39408,10 +39408,10 @@
         <v>0</v>
       </c>
       <c r="Y302" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z302" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA302" t="n">
         <v>0</v>
@@ -39462,7 +39462,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -39472,12 +39472,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39591,7 +39591,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39720,7 +39720,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39978,22 +39978,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40014,13 +40014,13 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M307" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O307" t="n">
         <v>0</v>
@@ -40053,10 +40053,10 @@
         <v>0</v>
       </c>
       <c r="Y307" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z307" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA307" t="n">
         <v>0</v>
@@ -40107,7 +40107,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40236,22 +40236,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40401,13 +40401,13 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N310" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
@@ -40440,10 +40440,10 @@
         <v>0</v>
       </c>
       <c r="Y310" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z310" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA310" t="n">
         <v>0</v>
@@ -40494,22 +40494,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40530,13 +40530,13 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N311" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -40569,10 +40569,10 @@
         <v>0</v>
       </c>
       <c r="Y311" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z311" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA311" t="n">
         <v>0</v>
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Retrô</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41397,7 +41397,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -41794,12 +41794,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -42042,7 +42042,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -42052,12 +42052,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42300,7 +42300,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -42568,12 +42568,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -42697,12 +42697,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Retrô</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -42826,12 +42826,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -43342,12 +43342,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -43368,22 +43368,22 @@
         </is>
       </c>
       <c r="L333" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M333" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N333" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O333" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P333" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q333" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R333" t="n">
         <v>0</v>
@@ -43407,10 +43407,10 @@
         <v>0</v>
       </c>
       <c r="Y333" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z333" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA333" t="n">
         <v>0</v>
@@ -43441,10 +43441,10 @@
         <v>0</v>
       </c>
       <c r="AI333" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ333" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK333" s="3" t="n">
         <v>45899.79166666666</v>
@@ -43471,12 +43471,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -43600,12 +43600,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -43729,12 +43729,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -43858,12 +43858,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -43987,12 +43987,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -44013,22 +44013,22 @@
         </is>
       </c>
       <c r="L338" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N338" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O338" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P338" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q338" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R338" t="n">
         <v>0</v>
@@ -44052,10 +44052,10 @@
         <v>0</v>
       </c>
       <c r="Y338" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z338" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA338" t="n">
         <v>0</v>
@@ -44086,10 +44086,10 @@
         <v>0</v>
       </c>
       <c r="AI338" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ338" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AK338" s="3" t="n">
         <v>45899.79166666666</v>
@@ -44116,12 +44116,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -44245,12 +44245,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -44364,7 +44364,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -44374,12 +44374,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -44493,7 +44493,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -44503,12 +44503,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -44632,12 +44632,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -44751,7 +44751,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -44787,13 +44787,13 @@
         </is>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M344" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N344" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O344" t="n">
         <v>0</v>
@@ -44832,10 +44832,10 @@
         <v>0</v>
       </c>
       <c r="AA344" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB344" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC344" t="n">
         <v>0</v>
@@ -44880,7 +44880,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -44890,12 +44890,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -45009,7 +45009,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -45019,12 +45019,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -45045,13 +45045,13 @@
         </is>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M346" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N346" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O346" t="n">
         <v>0</v>
@@ -45090,10 +45090,10 @@
         <v>0</v>
       </c>
       <c r="AA346" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB346" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC346" t="n">
         <v>0</v>
@@ -45148,12 +45148,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -45174,13 +45174,13 @@
         </is>
       </c>
       <c r="L347" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="M347" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N347" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="O347" t="n">
         <v>0</v>
@@ -45213,16 +45213,16 @@
         <v>0</v>
       </c>
       <c r="Y347" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z347" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA347" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB347" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC347" t="n">
         <v>0</v>
@@ -45267,7 +45267,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -45277,12 +45277,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -45396,7 +45396,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -45406,12 +45406,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -45432,13 +45432,13 @@
         </is>
       </c>
       <c r="L349" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M349" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N349" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O349" t="n">
         <v>0</v>
@@ -45477,10 +45477,10 @@
         <v>0</v>
       </c>
       <c r="AA349" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB349" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC349" t="n">
         <v>0</v>
@@ -45535,12 +45535,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G350" t="n">
@@ -45561,13 +45561,13 @@
         </is>
       </c>
       <c r="L350" t="n">
-        <v>2.09</v>
+        <v>2.39</v>
       </c>
       <c r="M350" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N350" t="n">
-        <v>2.95</v>
+        <v>2.47</v>
       </c>
       <c r="O350" t="n">
         <v>0</v>
@@ -45600,16 +45600,16 @@
         <v>0</v>
       </c>
       <c r="Y350" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z350" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA350" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB350" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC350" t="n">
         <v>0</v>
@@ -45654,7 +45654,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -45664,12 +45664,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -45690,13 +45690,13 @@
         </is>
       </c>
       <c r="L351" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N351" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O351" t="n">
         <v>0</v>
@@ -45729,10 +45729,10 @@
         <v>0</v>
       </c>
       <c r="Y351" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z351" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA351" t="n">
         <v>0</v>
@@ -45783,7 +45783,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -45793,12 +45793,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -45819,13 +45819,13 @@
         </is>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M352" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N352" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O352" t="n">
         <v>0</v>
@@ -45864,10 +45864,10 @@
         <v>0</v>
       </c>
       <c r="AA352" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB352" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC352" t="n">
         <v>0</v>
@@ -45912,7 +45912,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -45922,12 +45922,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -45948,13 +45948,13 @@
         </is>
       </c>
       <c r="L353" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N353" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O353" t="n">
         <v>0</v>
@@ -45993,10 +45993,10 @@
         <v>0</v>
       </c>
       <c r="AA353" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB353" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC353" t="n">
         <v>0</v>
@@ -46051,12 +46051,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -46077,13 +46077,13 @@
         </is>
       </c>
       <c r="L354" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="M354" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="N354" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="O354" t="n">
         <v>0</v>
@@ -46116,16 +46116,16 @@
         <v>0</v>
       </c>
       <c r="Y354" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z354" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA354" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB354" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC354" t="n">
         <v>0</v>
@@ -46438,12 +46438,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -46464,13 +46464,13 @@
         </is>
       </c>
       <c r="L357" t="n">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="M357" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N357" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="O357" t="n">
         <v>0</v>
@@ -46509,10 +46509,10 @@
         <v>2.3</v>
       </c>
       <c r="AA357" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB357" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC357" t="n">
         <v>0</v>
@@ -46567,12 +46567,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -46593,13 +46593,13 @@
         </is>
       </c>
       <c r="L358" t="n">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="M358" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="N358" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="O358" t="n">
         <v>0</v>
@@ -46696,12 +46696,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -46722,13 +46722,13 @@
         </is>
       </c>
       <c r="L359" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="M359" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="N359" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O359" t="n">
         <v>0</v>
@@ -46761,16 +46761,16 @@
         <v>0</v>
       </c>
       <c r="Y359" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA359" t="n">
         <v>2.3</v>
       </c>
-      <c r="AA359" t="n">
-        <v>0</v>
-      </c>
       <c r="AB359" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC359" t="n">
         <v>0</v>
@@ -46954,12 +46954,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -46980,13 +46980,13 @@
         </is>
       </c>
       <c r="L361" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="M361" t="n">
         <v>4</v>
       </c>
       <c r="N361" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O361" t="n">
         <v>0</v>
@@ -47019,16 +47019,16 @@
         <v>0</v>
       </c>
       <c r="Y361" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z361" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA361" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AB361" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC361" t="n">
         <v>0</v>
@@ -47083,12 +47083,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G362" t="n">
@@ -47212,12 +47212,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -47589,7 +47589,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -47599,12 +47599,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -47625,13 +47625,13 @@
         </is>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M366" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N366" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O366" t="n">
         <v>0</v>
@@ -47664,10 +47664,10 @@
         <v>0</v>
       </c>
       <c r="Y366" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z366" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA366" t="n">
         <v>0</v>
@@ -47718,7 +47718,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -47728,12 +47728,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -47754,13 +47754,13 @@
         </is>
       </c>
       <c r="L367" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N367" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O367" t="n">
         <v>0</v>
@@ -47799,10 +47799,10 @@
         <v>0</v>
       </c>
       <c r="AA367" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB367" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC367" t="n">
         <v>0</v>
@@ -47857,12 +47857,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -47883,13 +47883,13 @@
         </is>
       </c>
       <c r="L368" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M368" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="N368" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O368" t="n">
         <v>0</v>
@@ -47922,16 +47922,16 @@
         <v>0</v>
       </c>
       <c r="Y368" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z368" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA368" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB368" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC368" t="n">
         <v>0</v>
@@ -47986,12 +47986,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G369" t="n">
